--- a/services/cards.xlsx
+++ b/services/cards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Python Project\services\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A28AC793-1278-4644-AC2D-7F8C35470603}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49AFD0E0-6BBA-40EF-A9DB-F4032EC2B633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="28800" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cards" sheetId="1" r:id="rId1"/>
@@ -64,9 +64,6 @@
     <t>обычная капибара</t>
   </si>
   <si>
-    <t>Редкость(1 - 3)</t>
-  </si>
-  <si>
     <t>ТИП</t>
   </si>
   <si>
@@ -155,18 +152,29 @@
   </si>
   <si>
     <t xml:space="preserve"> @___ @    U^ｪ^U</t>
+  </si>
+  <si>
+    <t>Редкость</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -231,26 +239,29 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -754,32 +765,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -816,7 +827,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
@@ -932,7 +943,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>13</v>
@@ -953,7 +964,7 @@
         <v>70</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -964,7 +975,7 @@
         <v>8</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -982,7 +993,7 @@
         <v>200</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="16.5">
@@ -993,7 +1004,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -1022,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1048,10 +1059,10 @@
         <v>2</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1069,7 +1080,7 @@
         <v>300</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1077,10 +1088,10 @@
         <v>2</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>30</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>31</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1098,7 +1109,7 @@
         <v>250</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1109,7 +1120,7 @@
         <v>8</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -1135,10 +1146,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>34</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>35</v>
       </c>
       <c r="D14">
         <v>35</v>
@@ -1164,10 +1175,10 @@
         <v>3</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1185,7 +1196,7 @@
         <v>800</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1193,10 +1204,10 @@
         <v>3</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1222,10 +1233,10 @@
         <v>3</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -1243,7 +1254,7 @@
         <v>700</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1251,10 +1262,10 @@
         <v>3</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -1272,7 +1283,7 @@
         <v>750</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/services/cards.xlsx
+++ b/services/cards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Python Project\services\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49AFD0E0-6BBA-40EF-A9DB-F4032EC2B633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{478EA938-87A2-462F-9831-330225D606DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="15" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4695" yWindow="1800" windowWidth="28800" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cards" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="46">
   <si>
     <t>security</t>
   </si>
@@ -28,39 +28,24 @@
     <t>обычный медведь</t>
   </si>
   <si>
-    <t>_/□\\_    ʕ•ᴥ•ʔ</t>
-  </si>
-  <si>
     <t>обычный кот</t>
   </si>
   <si>
-    <t>/\/\    ( •·•)</t>
-  </si>
-  <si>
     <t>buffer</t>
   </si>
   <si>
     <t>обычный кролик</t>
   </si>
   <si>
-    <t>/) /)    ( • ,•)</t>
-  </si>
-  <si>
     <t>deathrattle</t>
   </si>
   <si>
     <t>обычный мини-пиг</t>
   </si>
   <si>
-    <t>()____()     (^(oo)^)</t>
-  </si>
-  <si>
     <t>обычный воробей</t>
   </si>
   <si>
-    <t>_|¦|_    / * &gt;</t>
-  </si>
-  <si>
     <t>обычная капибара</t>
   </si>
   <si>
@@ -88,9 +73,6 @@
     <t>Энергия</t>
   </si>
   <si>
-    <t>△    /   * )</t>
-  </si>
-  <si>
     <t>Редкий мини-пиг</t>
   </si>
   <si>
@@ -115,9 +97,6 @@
     <t>редкий мистер карп</t>
   </si>
   <si>
-    <t>_|¯|_      (°)#))&lt;&lt;</t>
-  </si>
-  <si>
     <t>редкий воробей</t>
   </si>
   <si>
@@ -148,25 +127,57 @@
     <t>легендарный баран</t>
   </si>
   <si>
-    <t>_/‾\_    U'ᴥ'U</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> @___ @    U^ｪ^U</t>
-  </si>
-  <si>
     <t>Редкость</t>
+  </si>
+  <si>
+    <t>_|¦|_   / * &gt;</t>
+  </si>
+  <si>
+    <t>_/□\\_   ʕ•ᴥ•ʔ</t>
+  </si>
+  <si>
+    <t>/\/\   ( •·•)</t>
+  </si>
+  <si>
+    <t>/) /)   ( • ,•)</t>
+  </si>
+  <si>
+    <t>△   /   * )</t>
+  </si>
+  <si>
+    <t>()____()   (^(oo)^)</t>
+  </si>
+  <si>
+    <t>_|¯|_     (°)#))&lt;&lt;</t>
+  </si>
+  <si>
+    <t>_/‾\_   U'ᴥ'U</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> @___ @   U^ｪ^U</t>
+  </si>
+  <si>
+    <t>_|¦|_  / * &gt;</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -239,26 +250,29 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -765,32 +779,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="8" t="s">
-        <v>44</v>
+      <c r="A1" s="7" t="s">
+        <v>35</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="G1" s="4" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -819,7 +833,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>2</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -827,10 +841,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3">
         <v>20</v>
@@ -848,7 +862,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -856,10 +870,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -877,7 +891,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -885,10 +899,10 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -906,7 +920,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="1" customFormat="1" ht="14.25" customHeight="1">
@@ -914,10 +928,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D6" s="4">
         <v>0</v>
@@ -934,8 +948,8 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>12</v>
+      <c r="I6" s="9" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -943,10 +957,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
@@ -963,8 +977,8 @@
       <c r="H7" s="1">
         <v>70</v>
       </c>
-      <c r="I7" s="4" t="s">
-        <v>22</v>
+      <c r="I7" s="8" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -972,10 +986,10 @@
         <v>2</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -993,7 +1007,7 @@
         <v>200</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="16.5">
@@ -1001,10 +1015,10 @@
         <v>2</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -1021,8 +1035,8 @@
       <c r="H9">
         <v>250</v>
       </c>
-      <c r="I9" s="4" t="s">
-        <v>7</v>
+      <c r="I9" s="8" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1033,7 +1047,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1051,7 +1065,7 @@
         <v>300</v>
       </c>
       <c r="I10" t="s">
-        <v>2</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1059,10 +1073,10 @@
         <v>2</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1079,8 +1093,8 @@
       <c r="H11">
         <v>300</v>
       </c>
-      <c r="I11" s="4" t="s">
-        <v>22</v>
+      <c r="I11" s="8" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1088,10 +1102,10 @@
         <v>2</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1108,8 +1122,8 @@
       <c r="H12">
         <v>250</v>
       </c>
-      <c r="I12" s="4" t="s">
-        <v>31</v>
+      <c r="I12" s="8" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -1117,10 +1131,10 @@
         <v>2</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -1137,8 +1151,8 @@
       <c r="H13">
         <v>450</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>12</v>
+      <c r="I13" s="8" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -1146,10 +1160,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D14">
         <v>35</v>
@@ -1167,7 +1181,7 @@
         <v>900</v>
       </c>
       <c r="I14" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1175,10 +1189,10 @@
         <v>3</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1195,8 +1209,8 @@
       <c r="H15">
         <v>800</v>
       </c>
-      <c r="I15" s="4" t="s">
-        <v>42</v>
+      <c r="I15" s="8" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1204,10 +1218,10 @@
         <v>3</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1225,7 +1239,7 @@
         <v>1000</v>
       </c>
       <c r="I16" t="s">
-        <v>2</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1233,10 +1247,10 @@
         <v>3</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -1253,8 +1267,8 @@
       <c r="H17">
         <v>700</v>
       </c>
-      <c r="I17" s="4" t="s">
-        <v>31</v>
+      <c r="I17" s="8" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -1262,10 +1276,10 @@
         <v>3</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -1282,8 +1296,8 @@
       <c r="H18">
         <v>750</v>
       </c>
-      <c r="I18" s="7" t="s">
-        <v>43</v>
+      <c r="I18" s="8" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/services/cards.xlsx
+++ b/services/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Python Project\services\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{478EA938-87A2-462F-9831-330225D606DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E025E5B2-2C72-44AD-AF51-3B9EB637EE4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4695" yWindow="1800" windowWidth="28800" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -133,51 +133,43 @@
     <t>_|¦|_   / * &gt;</t>
   </si>
   <si>
-    <t>_/□\\_   ʕ•ᴥ•ʔ</t>
-  </si>
-  <si>
-    <t>/\/\   ( •·•)</t>
-  </si>
-  <si>
-    <t>/) /)   ( • ,•)</t>
-  </si>
-  <si>
-    <t>△   /   * )</t>
-  </si>
-  <si>
-    <t>()____()   (^(oo)^)</t>
-  </si>
-  <si>
-    <t>_|¯|_     (°)#))&lt;&lt;</t>
-  </si>
-  <si>
-    <t>_/‾\_   U'ᴥ'U</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> @___ @   U^ｪ^U</t>
-  </si>
-  <si>
-    <t>_|¦|_  / * &gt;</t>
+    <t>_/□\\_    ʕ•ᴥ•ʔ</t>
+  </si>
+  <si>
+    <t>/\/\    ( •·•)</t>
+  </si>
+  <si>
+    <t>/) /)    ( • ,•)</t>
+  </si>
+  <si>
+    <t>()____()     (^(oo)^)</t>
+  </si>
+  <si>
+    <t>△    /   * )</t>
+  </si>
+  <si>
+    <t>_|¯|_      (°)#))&lt;&lt;</t>
+  </si>
+  <si>
+    <t>_|¦|_    / * &gt;</t>
+  </si>
+  <si>
+    <t>_/‾\_    U'ᴥ'U</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> @___ @    U^ｪ^U</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -250,29 +242,26 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -920,7 +909,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="1" customFormat="1" ht="14.25" customHeight="1">
@@ -948,8 +937,8 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6" s="9" t="s">
-        <v>45</v>
+      <c r="I6" s="8" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -978,7 +967,7 @@
         <v>70</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1007,7 +996,7 @@
         <v>200</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="16.5">
@@ -1094,7 +1083,7 @@
         <v>300</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1152,7 +1141,7 @@
         <v>450</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -1210,7 +1199,7 @@
         <v>800</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -1297,7 +1286,7 @@
         <v>750</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/services/cards.xlsx
+++ b/services/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Python Project\services\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E025E5B2-2C72-44AD-AF51-3B9EB637EE4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A79AD13-2F3A-42AD-8F86-D1B13894D523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4695" yWindow="1800" windowWidth="28800" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -76,9 +76,6 @@
     <t>Редкий мини-пиг</t>
   </si>
   <si>
-    <t>()____()    (^(oo)^)</t>
-  </si>
-  <si>
     <t>редкий кролик</t>
   </si>
   <si>
@@ -130,34 +127,37 @@
     <t>Редкость</t>
   </si>
   <si>
-    <t>_|¦|_   / * &gt;</t>
-  </si>
-  <si>
-    <t>_/□\\_    ʕ•ᴥ•ʔ</t>
-  </si>
-  <si>
-    <t>/\/\    ( •·•)</t>
-  </si>
-  <si>
-    <t>/) /)    ( • ,•)</t>
-  </si>
-  <si>
-    <t>()____()     (^(oo)^)</t>
-  </si>
-  <si>
-    <t>△    /   * )</t>
-  </si>
-  <si>
-    <t>_|¯|_      (°)#))&lt;&lt;</t>
-  </si>
-  <si>
-    <t>_|¦|_    / * &gt;</t>
-  </si>
-  <si>
-    <t>_/‾\_    U'ᴥ'U</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> @___ @    U^ｪ^U</t>
+    <t xml:space="preserve"> _/□\\_    ʕ•ᴥ•ʔ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> /\/\    ( •·•)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> /) /)    ( • ,•)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ()____()     (^(oo)^)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> _|¦|_   / * &gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> △    /   * )</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ()____()    (^(oo)^)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> _|¯|_      (°)#))&lt;&lt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> _|¦|_    / * &gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> _/‾\_    U'ᴥ'U</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  @___ @    U^ｪ^U</t>
   </si>
 </sst>
 </file>
@@ -769,7 +769,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>9</v>
@@ -822,7 +822,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -830,7 +830,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>2</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -880,7 +880,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -909,7 +909,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="1" customFormat="1" ht="14.25" customHeight="1">
@@ -938,7 +938,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -946,7 +946,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>70</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -996,7 +996,7 @@
         <v>200</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="16.5">
@@ -1007,7 +1007,7 @@
         <v>3</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -1025,7 +1025,7 @@
         <v>250</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1054,7 +1054,7 @@
         <v>300</v>
       </c>
       <c r="I10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1062,10 +1062,10 @@
         <v>2</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1083,7 +1083,7 @@
         <v>300</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -1091,10 +1091,10 @@
         <v>2</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>24</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1123,7 +1123,7 @@
         <v>5</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -1149,10 +1149,10 @@
         <v>3</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>26</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="D14">
         <v>35</v>
@@ -1170,7 +1170,7 @@
         <v>900</v>
       </c>
       <c r="I14" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -1178,10 +1178,10 @@
         <v>3</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1207,10 +1207,10 @@
         <v>3</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1228,7 +1228,7 @@
         <v>1000</v>
       </c>
       <c r="I16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -1236,10 +1236,10 @@
         <v>3</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -1265,10 +1265,10 @@
         <v>3</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18">
         <v>1</v>

--- a/services/cards.xlsx
+++ b/services/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Python Project\services\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A79AD13-2F3A-42AD-8F86-D1B13894D523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CA75CE4-9BAE-41F2-A28B-D54C0F4E5928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4695" yWindow="1800" windowWidth="28800" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="47">
   <si>
     <t>security</t>
   </si>
@@ -158,6 +158,9 @@
   </si>
   <si>
     <t xml:space="preserve">  @___ @    U^ｪ^U</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> /\/\   ( •·•)</t>
   </si>
 </sst>
 </file>
@@ -851,7 +854,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:9">

--- a/services/cards.xlsx
+++ b/services/cards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Python Project\services\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CA75CE4-9BAE-41F2-A28B-D54C0F4E5928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E43F271F-C36C-4C25-9CC1-4E537F85EBB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4695" yWindow="1800" windowWidth="28800" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8865" yWindow="5940" windowWidth="28800" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cards" sheetId="1" r:id="rId1"/>
@@ -822,7 +822,7 @@
         <v>4</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I2" t="s">
         <v>35</v>
@@ -851,7 +851,7 @@
         <v>3</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I3" t="s">
         <v>46</v>
@@ -880,7 +880,7 @@
         <v>3</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I4" t="s">
         <v>37</v>
@@ -909,7 +909,7 @@
         <v>2</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="I5" t="s">
         <v>38</v>
@@ -938,7 +938,7 @@
         <v>1</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I6" s="8" t="s">
         <v>39</v>

--- a/services/cards.xlsx
+++ b/services/cards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Python Project\services\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E43F271F-C36C-4C25-9CC1-4E537F85EBB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4974864A-28CA-437F-B066-963E0A5BF999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8865" yWindow="5940" windowWidth="28800" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3855" yWindow="5250" windowWidth="30120" windowHeight="14070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cards" sheetId="1" r:id="rId1"/>

--- a/services/cards.xlsx
+++ b/services/cards.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Python Project\services\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4974864A-28CA-437F-B066-963E0A5BF999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E628C6-B3DE-42B8-98F5-62EF521FD8CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3855" yWindow="5250" windowWidth="30120" windowHeight="14070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cards" sheetId="1" r:id="rId1"/>

--- a/services/cards.xlsx
+++ b/services/cards.xlsx
@@ -1,26 +1,60 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Python Project\services\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B16199D-6D80-468F-A0CE-6B5CE66BABE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4305" yWindow="3435" windowWidth="28800" windowHeight="15885" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="21600" windowHeight="9555"/>
   </bookViews>
   <sheets>
     <sheet name="cards" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="46">
+  <si>
+    <t>Редкость(1 - 3)</t>
+  </si>
+  <si>
+    <t>ТИП</t>
+  </si>
+  <si>
+    <t>ИМЯ</t>
+  </si>
+  <si>
+    <t>сила способности</t>
+  </si>
+  <si>
+    <t>ХП</t>
+  </si>
+  <si>
+    <t>урон</t>
+  </si>
+  <si>
+    <t>Энергия</t>
+  </si>
+  <si>
+    <t>ЦЕНА</t>
+  </si>
+  <si>
+    <t>Иконка</t>
+  </si>
   <si>
     <t>security</t>
   </si>
@@ -31,6 +65,9 @@
     <t>_/□\\_    ʕ•ᴥ•ʔ</t>
   </si>
   <si>
+    <t>attack</t>
+  </si>
+  <si>
     <t>обычный кот</t>
   </si>
   <si>
@@ -55,42 +92,21 @@
     <t>()____()     (^(oo)^)</t>
   </si>
   <si>
+    <t>default</t>
+  </si>
+  <si>
     <t>обычный воробей</t>
   </si>
   <si>
     <t>_|¦|_    / * &gt;</t>
   </si>
   <si>
+    <t>impaler</t>
+  </si>
+  <si>
     <t>обычная капибара</t>
   </si>
   <si>
-    <t>Редкость(1 - 3)</t>
-  </si>
-  <si>
-    <t>ТИП</t>
-  </si>
-  <si>
-    <t>ИМЯ</t>
-  </si>
-  <si>
-    <t>Иконка</t>
-  </si>
-  <si>
-    <t>ЦЕНА</t>
-  </si>
-  <si>
-    <t>сила способности</t>
-  </si>
-  <si>
-    <t>ХП</t>
-  </si>
-  <si>
-    <t>урон</t>
-  </si>
-  <si>
-    <t>Энергия</t>
-  </si>
-  <si>
     <t>△    /   * )</t>
   </si>
   <si>
@@ -103,9 +119,6 @@
     <t>редкий кролик</t>
   </si>
   <si>
-    <t>impaler</t>
-  </si>
-  <si>
     <t>Редкий медведь</t>
   </si>
   <si>
@@ -124,37 +137,31 @@
     <t>редкий воробей</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>attack</t>
-  </si>
-  <si>
     <t>легендарный кот</t>
   </si>
   <si>
     <t>twins</t>
   </si>
   <si>
+    <t>легендарный пес</t>
+  </si>
+  <si>
+    <t>_/‾\_    U'ᴥ'U</t>
+  </si>
+  <si>
+    <t>security attack</t>
+  </si>
+  <si>
+    <t>легендарный медведь</t>
+  </si>
+  <si>
+    <t>легендарный мистер карп</t>
+  </si>
+  <si>
     <t>blitz</t>
   </si>
   <si>
-    <t>легендарный пес</t>
-  </si>
-  <si>
-    <t>легендарный медведь</t>
-  </si>
-  <si>
-    <t>security attack</t>
-  </si>
-  <si>
-    <t>легендарный мистер карп</t>
-  </si>
-  <si>
     <t>легендарный баран</t>
-  </si>
-  <si>
-    <t>_/‾\_    U'ᴥ'U</t>
   </si>
   <si>
     <t xml:space="preserve"> @___ @    U^ｪ^U</t>
@@ -163,8 +170,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-* #\.##0.00_-;\-* #\.##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-* #\.##0.00\ &quot;₽&quot;_-;\-* #\.##0.00\ &quot;₽&quot;_-;_-* \-??\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -176,15 +189,19 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <color rgb="FF111111"/>
+      <name val="Rubik"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF111111"/>
+      <name val="Calibri"/>
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
@@ -192,35 +209,354 @@
       <sz val="8"/>
       <color rgb="FF111111"/>
       <name val="Rubik"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF111111"/>
-      <name val="Rubik"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF111111"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="13"/>
       <color rgb="FF111111"/>
       <name val="Rubik"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -228,190 +564,360 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Запятая" xfId="1" builtinId="3"/>
+    <cellStyle name="Денежный" xfId="2" builtinId="4"/>
+    <cellStyle name="Процент" xfId="3" builtinId="5"/>
+    <cellStyle name="Запятая [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Денежный [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Гиперссылка" xfId="6" builtinId="8"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="7" builtinId="9"/>
+    <cellStyle name="Примечание" xfId="8" builtinId="10"/>
+    <cellStyle name="Предупреждающий текст" xfId="9" builtinId="11"/>
+    <cellStyle name="Заголовок" xfId="10" builtinId="15"/>
+    <cellStyle name="Пояснительный текст" xfId="11" builtinId="53"/>
+    <cellStyle name="Заголовок 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Заголовок 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Заголовок 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Заголовок 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Ввод" xfId="16" builtinId="20"/>
+    <cellStyle name="Вывод" xfId="17" builtinId="21"/>
+    <cellStyle name="Вычисление" xfId="18" builtinId="22"/>
+    <cellStyle name="Проверить ячейку" xfId="19" builtinId="23"/>
+    <cellStyle name="Связанная ячейка" xfId="20" builtinId="24"/>
+    <cellStyle name="Итого" xfId="21" builtinId="25"/>
+    <cellStyle name="Хороший" xfId="22" builtinId="26"/>
+    <cellStyle name="Плохой" xfId="23" builtinId="27"/>
+    <cellStyle name="Нейтральный" xfId="24" builtinId="28"/>
+    <cellStyle name="Акцент1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% — Акцент1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% — Акцент1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% — Акцент1" xfId="28" builtinId="32"/>
+    <cellStyle name="Акцент2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% — Акцент2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% — Акцент2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% — Акцент2" xfId="32" builtinId="36"/>
+    <cellStyle name="Акцент3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% — Акцент3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% — Акцент3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% — Акцент3" xfId="36" builtinId="40"/>
+    <cellStyle name="Акцент4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% — Акцент4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% — Акцент4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% — Акцент4" xfId="40" builtinId="44"/>
+    <cellStyle name="Акцент5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% — Акцент5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% — Акцент5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% — Акцент5" xfId="44" builtinId="48"/>
+    <cellStyle name="Акцент6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% — Акцент6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% — Акцент6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% — Акцент6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
       <border>
@@ -422,7 +928,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -450,40 +956,154 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
+          <color theme="4" tint="0.399975585192419"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
-      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -741,48 +1361,49 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultColWidth="10.28515625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.140625" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" customWidth="1"/>
-    <col min="3" max="3" width="27.140625" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" customWidth="1"/>
+    <col min="1" max="1" width="15.1428571428571" customWidth="1"/>
+    <col min="2" max="2" width="15.7142857142857" customWidth="1"/>
+    <col min="3" max="3" width="27.1428571428571" customWidth="1"/>
+    <col min="4" max="4" width="16.5714285714286" customWidth="1"/>
+    <col min="9" max="9" width="20.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>17</v>
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -790,10 +1411,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -811,18 +1432,18 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>35</v>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D3">
         <v>20</v>
@@ -840,7 +1461,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -848,10 +1469,10 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -869,18 +1490,18 @@
         <v>0</v>
       </c>
       <c r="I4" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" ht="19" customHeight="1" spans="1:9">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -898,21 +1519,21 @@
         <v>0</v>
       </c>
       <c r="I5" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:9" s="1" customFormat="1" ht="33" customHeight="1">
+    <row r="6" s="1" customFormat="1" ht="18" customHeight="1" spans="1:9">
       <c r="A6">
         <v>1</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>34</v>
+      <c r="B6" s="2" t="s">
+        <v>21</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>34</v>
+        <v>22</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -926,8 +1547,8 @@
       <c r="H6">
         <v>0</v>
       </c>
-      <c r="I6" s="4" t="s">
-        <v>12</v>
+      <c r="I6" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -935,10 +1556,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="D7" s="1">
         <v>1</v>
@@ -955,19 +1576,19 @@
       <c r="H7" s="1">
         <v>70</v>
       </c>
-      <c r="I7" s="4" t="s">
-        <v>23</v>
+      <c r="I7" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8">
         <v>2</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>24</v>
+      <c r="B8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -984,19 +1605,19 @@
       <c r="H8">
         <v>200</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>25</v>
+      <c r="I8" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="16.5">
+    <row r="9" ht="16.5" spans="1:9">
       <c r="A9">
         <v>2</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>26</v>
+        <v>15</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="D9">
         <v>2</v>
@@ -1013,8 +1634,8 @@
       <c r="H9">
         <v>250</v>
       </c>
-      <c r="I9" s="4" t="s">
-        <v>7</v>
+      <c r="I9" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1022,10 +1643,10 @@
         <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -1043,7 +1664,7 @@
         <v>300</v>
       </c>
       <c r="I10" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1051,10 +1672,10 @@
         <v>2</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>29</v>
+        <v>24</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -1071,19 +1692,19 @@
       <c r="H11">
         <v>300</v>
       </c>
-      <c r="I11" s="4" t="s">
-        <v>23</v>
+      <c r="I11" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12">
         <v>2</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>31</v>
+      <c r="B12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -1100,19 +1721,19 @@
       <c r="H12">
         <v>250</v>
       </c>
-      <c r="I12" s="4" t="s">
-        <v>32</v>
+      <c r="I12" s="2" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13">
         <v>2</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>33</v>
+      <c r="B13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -1129,18 +1750,18 @@
       <c r="H13">
         <v>450</v>
       </c>
-      <c r="I13" s="4" t="s">
-        <v>12</v>
+      <c r="I13" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14">
         <v>3</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="4" t="s">
+      <c r="B14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>36</v>
       </c>
       <c r="D14">
@@ -1159,18 +1780,18 @@
         <v>900</v>
       </c>
       <c r="I14" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15">
         <v>3</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>39</v>
+      <c r="C15" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -1187,19 +1808,19 @@
       <c r="H15">
         <v>800</v>
       </c>
-      <c r="I15" s="4" t="s">
-        <v>44</v>
+      <c r="I15" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16">
         <v>3</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>40</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1217,17 +1838,17 @@
         <v>1000</v>
       </c>
       <c r="I16" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17">
         <v>3</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" s="4" t="s">
+      <c r="B17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D17">
@@ -1245,19 +1866,19 @@
       <c r="H17">
         <v>700</v>
       </c>
-      <c r="I17" s="4" t="s">
-        <v>32</v>
+      <c r="I17" s="2" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18">
         <v>3</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" s="4" t="s">
+      <c r="B18" s="2" t="s">
         <v>43</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -1274,11 +1895,12 @@
       <c r="H18">
         <v>750</v>
       </c>
-      <c r="I18" s="7" t="s">
+      <c r="I18" s="2" t="s">
         <v>45</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/services/cards.xlsx
+++ b/services/cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Python Project\services\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58E628C6-B3DE-42B8-98F5-62EF521FD8CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9A42F14-25EF-497F-AB5A-F13E70C899EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
